--- a/Padrao/Leiautes/Tabela de Preços/Dotações/PRESTADOR/SAM_PRECOPRESTADOR_DOTAC.xlsx
+++ b/Padrao/Leiautes/Tabela de Preços/Dotações/PRESTADOR/SAM_PRECOPRESTADOR_DOTAC.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12504" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12504"/>
   </bookViews>
   <sheets>
     <sheet name="SAM_PRECOPRESTADOR_DOTAC" sheetId="1" r:id="rId1"/>
@@ -26,13 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="132">
-  <si>
-    <t>SAM_PRECOPRESTADOR_DOTAC</t>
-  </si>
-  <si>
-    <t>TABELA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="134">
   <si>
     <t>CAMPO</t>
   </si>
@@ -224,15 +218,6 @@
   </si>
   <si>
     <t>Porte de sala da dotação</t>
-  </si>
-  <si>
-    <t>PRESTADOR</t>
-  </si>
-  <si>
-    <t>Prestador</t>
-  </si>
-  <si>
-    <t>SAM_PRESTADOR</t>
   </si>
   <si>
     <t>QTDUSCUSTOOPERACIONAL</t>
@@ -315,9 +300,6 @@
     <t>Se TABNEGOCIACAO = 2</t>
   </si>
   <si>
-    <t>Se 2, exigira o preenchimento de  DEANOS, DEDIAS , ATEANOS, ATEDIAS</t>
-  </si>
-  <si>
     <t>Convênio do preço fixo 1</t>
   </si>
   <si>
@@ -333,9 +315,6 @@
     <t>campo MASCARATGE contido na extração de TGE, para evitar problema de duplicidade de estrutura</t>
   </si>
   <si>
-    <t>Prestador do preço Informar Codigo do Prestador definido na extração de Prestador (CAMPO PRESTADOR)</t>
-  </si>
-  <si>
     <t>HANDLE</t>
   </si>
   <si>
@@ -430,13 +409,44 @@
   </si>
   <si>
     <t>Informe a tabela a ser utilizada para a US de honorários -  Fixo 1 pois tabela de honorarios sempre vai ser Real</t>
+  </si>
+  <si>
+    <t>NIVEL</t>
+  </si>
+  <si>
+    <t>Nivel de associação da tabela generica</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>P - PRESTADOR
+E - ESTADO
+G -  GERAL</t>
+  </si>
+  <si>
+    <t>CHAVE</t>
+  </si>
+  <si>
+    <t>Chave de Busca de acordo com o Nivel Definido</t>
+  </si>
+  <si>
+    <t>Se Nivel = P - então informar o codigo do prestador no qual será associado a tabela de preço
+Se Nivel = E - então informar a sigla do estado no qual será associada a tabela de preço;
+Se nivel = G - Enviar Vazio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se 2, exigira o preenchimento de  DEANOS, DEDIAS , ATEANOS, ATEDIAS - Parametrização útil apenas para o NIVEL = P - Prestador </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se TABNEGOCIACAO = 2 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,6 +465,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -481,13 +499,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -769,738 +793,685 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.33203125" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="6" max="6" width="25.21875" customWidth="1"/>
-    <col min="10" max="10" width="25.21875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="44.109375" customWidth="1"/>
+    <col min="5" max="5" width="25.21875" customWidth="1"/>
+    <col min="9" max="9" width="25.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
         <v>91</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="K12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="K13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="K14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="K15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="K16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4">
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
+        <v>12</v>
+      </c>
+      <c r="K19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
+      </c>
+      <c r="K20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="D21" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11">
-        <v>20</v>
-      </c>
-      <c r="I11" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12">
-        <v>6</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>97</v>
-      </c>
-      <c r="L12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13">
-        <v>3</v>
-      </c>
-      <c r="E13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13">
-        <v>5</v>
-      </c>
-      <c r="L13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14">
-        <v>3</v>
-      </c>
-      <c r="E14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14">
-        <v>5</v>
-      </c>
-      <c r="L14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15">
-        <v>5</v>
-      </c>
-      <c r="L15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
-      <c r="E16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16">
-        <v>5</v>
-      </c>
-      <c r="L16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19">
-        <v>6</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>68</v>
-      </c>
-      <c r="L19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20">
-        <v>3</v>
-      </c>
-      <c r="E20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20">
-        <v>12</v>
-      </c>
-      <c r="L20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
         <v>72</v>
       </c>
-      <c r="C21" t="s">
+      <c r="K21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21">
-        <v>12</v>
-      </c>
-      <c r="L21" t="s">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>0</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s">
         <v>76</v>
       </c>
-      <c r="D22">
-        <v>6</v>
-      </c>
-      <c r="E22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="K22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="L22" s="3" t="s">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>0</v>
       </c>
       <c r="B23" t="s">
         <v>79</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
         <v>80</v>
       </c>
-      <c r="D23">
-        <v>6</v>
-      </c>
-      <c r="E23" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23">
+      <c r="K23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24">
         <v>10</v>
       </c>
-      <c r="I23" t="s">
-        <v>81</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="D24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="5">
         <v>0</v>
       </c>
-      <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24">
-        <v>6</v>
-      </c>
-      <c r="E24" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="s">
-        <v>85</v>
-      </c>
-      <c r="L24" t="s">
+      <c r="D25" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25">
-        <v>10</v>
-      </c>
-      <c r="E25" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K25" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L22" location="'Tabela de Custo Operacional'!A1" display="Informe a Tabela de custo operacional"/>
-    <hyperlink ref="L23" location="'Tabela de Filme'!A1" display="Informe o Código da Tabela de Filme"/>
+    <hyperlink ref="K21" location="'Tabela de Custo Operacional'!A1" display="Informe a Tabela de custo operacional"/>
+    <hyperlink ref="K22" location="'Tabela de Filme'!A1" display="Informe o Código da Tabela de Filme"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1514,10 +1485,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1525,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1533,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -1541,7 +1512,7 @@
         <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1549,7 +1520,7 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1557,7 +1528,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1565,7 +1536,7 @@
         <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1573,7 +1544,7 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1581,7 +1552,7 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1589,7 +1560,7 @@
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1597,7 +1568,7 @@
         <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1605,7 +1576,7 @@
         <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1613,7 +1584,7 @@
         <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -1621,7 +1592,7 @@
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -1629,7 +1600,7 @@
         <v>99</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -1637,7 +1608,7 @@
         <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1645,7 +1616,7 @@
         <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1653,7 +1624,7 @@
         <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -1661,7 +1632,7 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -1669,7 +1640,7 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -1677,7 +1648,7 @@
         <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -1685,7 +1656,7 @@
         <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -1693,7 +1664,7 @@
         <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -1701,7 +1672,7 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1717,10 +1688,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1728,7 +1699,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1736,7 +1707,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -1744,7 +1715,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1752,7 +1723,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1760,7 +1731,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1768,7 +1739,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1776,7 +1747,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1784,7 +1755,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1792,7 +1763,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1800,7 +1771,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1808,7 +1779,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1816,7 +1787,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
